--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_m_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_m_2018.xlsx
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:14</t>
+    <t xml:space="preserve">2026-10-05 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -710,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -718,7 +718,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -790,7 +790,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -846,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -910,7 +910,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -918,7 +918,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1030,7 +1030,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1118,7 +1118,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1126,7 +1126,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1158,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1174,7 +1174,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1214,7 +1214,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1286,7 +1286,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1310,7 +1310,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1318,7 +1318,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1334,7 +1334,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
